--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20211.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>SANDRIA</t>
+  </si>
+  <si>
     <t>NAVARRO</t>
   </si>
   <si>
@@ -97,6 +100,9 @@
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -107,6 +113,9 @@
   </si>
   <si>
     <t>ESTHER ARISBETH</t>
+  </si>
+  <si>
+    <t>MONSERRATH YARETZY</t>
   </si>
   <si>
     <t>DENISSE MERARY</t>
@@ -809,7 +818,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -847,10 +856,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -859,7 +868,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -870,10 +879,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -882,7 +891,7 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -893,10 +902,10 @@
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -905,7 +914,7 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -916,10 +925,10 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -928,30 +937,53 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920133</v>
+        <v>20330051920393</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920133</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="G6">
-        <v>6</v>
+      <c r="G7">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20211.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20211.xlsx
@@ -519,19 +519,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>69.44</v>
+        <v>72.22</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -636,16 +636,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>63.89</v>
+      </c>
+      <c r="H2">
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -659,16 +662,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.61</v>
+      </c>
+      <c r="H3">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -682,16 +688,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>86.95999999999999</v>
+      </c>
+      <c r="H4">
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -744,19 +753,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>69.44</v>
+        <v>72.22</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -808,7 +817,7 @@
         <v>86.95999999999999</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -983,7 +992,7 @@
         <v>12</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20211.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -79,46 +79,10 @@
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SANDRIA</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>KAREN</t>
-  </si>
-  <si>
-    <t>LUIS YAEL</t>
-  </si>
-  <si>
-    <t>ESTHER ARISBETH</t>
-  </si>
-  <si>
-    <t>MONSERRATH YARETZY</t>
-  </si>
-  <si>
-    <t>DENISSE MERARY</t>
   </si>
 </sst>
 </file>
@@ -519,19 +483,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -571,10 +535,10 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>20</v>
@@ -583,7 +547,7 @@
         <v>86.95999999999999</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -636,19 +600,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>63.89</v>
+        <v>83.33</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -662,19 +626,19 @@
         <v>23</v>
       </c>
       <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
         <v>3</v>
       </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
       <c r="F3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>82.61</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -688,19 +652,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>86.95999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -753,19 +717,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>72.22</v>
+        <v>83.33</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -805,19 +769,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4">
-        <v>86.95999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -827,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -865,10 +829,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -877,7 +841,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -888,10 +852,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -900,98 +864,6 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920156</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920179</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920393</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920133</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
         <v>3</v>
       </c>
     </row>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20211.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,13 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>KAREN</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>IRIS VIANNEY</t>
   </si>
 </sst>
 </file>
@@ -626,19 +626,19 @@
         <v>23</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
       <c r="F3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>86.95999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -652,7 +652,7 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -664,7 +664,7 @@
         <v>91.3</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -720,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>83.33</v>
+        <v>91.67</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -746,16 +746,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -772,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -791,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -823,7 +823,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920130</v>
+        <v>20330051920181</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -835,36 +835,13 @@
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920130</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez López Miguel Ángel - Estadisticos 20211.xlsx
+++ b/docentes/Martínez López Miguel Ángel - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -74,15 +74,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>IRIS VIANNEY</t>
   </si>
 </sst>
 </file>
@@ -720,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -791,7 +782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -821,29 +812,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920181</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
